--- a/artfynd/A 43385-2024 artfynd.xlsx
+++ b/artfynd/A 43385-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80083782</v>
+        <v>80083790</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387637.2221334791</v>
+        <v>387632</v>
       </c>
       <c r="R2" t="n">
-        <v>6701639.137884765</v>
+        <v>6701622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +743,18 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80083790</v>
+        <v>80083784</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387632.2378644771</v>
+        <v>387700</v>
       </c>
       <c r="R3" t="n">
-        <v>6701622.003603711</v>
+        <v>6701494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,28 +841,17 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,37 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80083784</v>
+        <v>80083782</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387700.012267334</v>
+        <v>387637</v>
       </c>
       <c r="R4" t="n">
-        <v>6701493.938908591</v>
+        <v>6701639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,19 +938,9 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,12 +970,7 @@
         <v>80083783</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387624.8126310299</v>
+        <v>387625</v>
       </c>
       <c r="R5" t="n">
-        <v>6701605.932876772</v>
+        <v>6701606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,19 +1035,9 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43385-2024 artfynd.xlsx
+++ b/artfynd/A 43385-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80083790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80083784</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80083782</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,8 +1081,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80083783</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>